--- a/tiflow-diga/develop/0.9.0/all-profiles.xlsx
+++ b/tiflow-diga/develop/0.9.0/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6178" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6165" uniqueCount="702">
   <si>
     <t>Property</t>
   </si>
@@ -740,9 +740,6 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>Communication.instantiatesUri</t>
   </si>
   <si>
@@ -773,10 +770,6 @@
   </si>
   <si>
     <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Communication.basedOn.id</t>
@@ -873,9 +866,6 @@
     <t>Part of this action.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Communication.inResponseTo</t>
   </si>
   <si>
@@ -990,9 +980,6 @@
     <t>A channel that was used for this communication (e.g. email, fax).</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
   </si>
   <si>
@@ -1236,9 +1223,6 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>GEM-ERP-PR-MedicationDispense-DiGA</t>
   </si>
   <si>
@@ -1335,7 +1319,7 @@
     <t>MedicationDispense.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1370,7 +1354,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -1391,7 +1375,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -1401,9 +1385,6 @@
   </si>
   <si>
     <t>MedicationDispense.language</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>MedicationDispense.text</t>
@@ -1509,10 +1490,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+    <t>External identifier</t>
   </si>
   <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
@@ -1530,9 +1508,6 @@
 </t>
   </si>
   <si>
-    <t>External identifier</t>
-  </si>
-  <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="https://gematik.de/fhir/erp/NamingSystem/GEM_ERP_NS_PrescriptionId"/&gt;
 &lt;/valueIdentifier&gt;</t>
@@ -1541,7 +1516,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure)
+    <t xml:space="preserve">Reference(Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1551,6 +1526,13 @@
     <t>The procedure that trigger the dispense.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>MedicationDispense.status</t>
   </si>
   <si>
@@ -1563,9 +1545,6 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the dispense event.</t>
-  </si>
-  <si>
     <t>https://gematik.de/fhir/terminology/ValueSet/ti-medication-dispense-status-vs</t>
   </si>
   <si>
@@ -1573,7 +1552,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>Why a dispense was not performed</t>
@@ -1585,7 +1564,7 @@
     <t>A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>MedicationDispense.category</t>
@@ -1671,10 +1650,17 @@
     <t>MedicationDispense.medication[x].extension.value[x]</t>
   </si>
   <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
     <t>asked-declined</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t>MedicationDispense.medication[x].reference</t>
@@ -1798,15 +1784,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>MedicationDispense.medication[x].identifier.assigner</t>
@@ -1862,9 +1840,6 @@
     <t>MedicationDispense.subject.type</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
-  </si>
-  <si>
     <t>MedicationDispense.subject.identifier</t>
   </si>
   <si>
@@ -1874,7 +1849,7 @@
     <t>MedicationDispense.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1887,10 +1862,6 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
-</t>
-  </si>
-  <si>
     <t>Information that supports the dispensing of the medication</t>
   </si>
   <si>
@@ -1924,13 +1895,16 @@
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
   </si>
   <si>
     <t>A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>MedicationDispense.performer.actor</t>
@@ -1967,7 +1941,7 @@
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1980,7 +1954,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -2026,7 +2000,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -2086,7 +2060,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
 </t>
   </si>
   <si>
@@ -2103,6 +2077,9 @@
   </si>
   <si>
     <t>Extra information about the dispense that could not be conveyed in the other attributes.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>MedicationDispense.dosageInstruction</t>
@@ -2119,123 +2096,6 @@
 The pharmacist reviews the medication order prior to dispense and updates the dosageInstruction based on the actual product being dispensed.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-DosageStructuredOrFreeTextWarning:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresBoth:Wenn eine strukturierte Dosierungsangabe erfolgt, müssen sowohl timing als auch doseAndRate angegeben werden. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (timing.exists() implies doseAndRate.exists()) and
-  (doseAndRate.exists() implies timing.exists())
-)
-}DosageDoseUnitSameCode:Die Dosiereinheit muss über alle Dosierungen gleich sein. {(%resource.ofType(MedicationRequest).dosageInstruction | ofType(MedicationDispense).dosageInstruction | ofType(MedicationStatement).dosage).all(
-doseAndRate.exists() implies
-  (
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Quantity).code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).low.code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).high.code
-  ).distinct().count() = 1
-)}DosageWarnungViererschemaInText:Hinweis: In Dosage.text wurde ein Viererschema (z. B. 1-1-1-1) erkannt. Bitte prüfen, ob dies strukturiert abgebildet werden kann. {text.exists() implies text.matches('.*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\d+.*').not()}FreeTextSingleDosageOnlyWarning:Wenn eine Dosierung als reiner Freitext angegeben ist, soll nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}DosageStructuredOrFreeText:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresGeneratedText:Liegt eine strukturierte Dosierungsangabe vor (timing und doseAndRate belegt, text leer), muss die Extension GeneratedDosageInstructionsMeta vorhanden sein. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(timing.exists() and doseAndRate.exists() and text.empty())
-)
-implies
-(
-%resource.extension.where(
-  url = 'http://ig.fhir.de/igs/medication/StructureDefinition/GeneratedDosageInstructionsMeta'
-).exists() and
-(
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-  ).exists()
-)
-)
-}FreeTextSingleDosageOnly:Wenn eine Dosierung als reiner Freitext angegeben ist, darf nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}FreeTextMatchesRenderedText:Wenn eine Dosierung als reiner Freitext angegeben ist (text vorhanden, timing und doseAndRate leer) UND die Extension renderedDosageInstruction befüllt ist, muss der Wert in dosageInstruction.text mit dem Wert in der Extension übereinstimmen. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).where(text.exists() and timing.empty() and doseAndRate.empty()).exists()
-)
-implies
-(
-  (
-    %resource.ofType(MedicationRequest).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationDispense).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationStatement).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).value = %resource.dosage.text
-    )
-  )
-)}</t>
-  </si>
-  <si>
     <t>MedicationDispense.substitution</t>
   </si>
   <si>
@@ -2303,7 +2163,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -2320,7 +2180,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -2336,7 +2196,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -3164,7 +3024,7 @@
         <v>2</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="89">
@@ -3172,7 +3032,7 @@
         <v>4</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="90">
@@ -3188,7 +3048,7 @@
         <v>8</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="92">
@@ -3196,7 +3056,7 @@
         <v>10</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="93">
@@ -3250,7 +3110,7 @@
         <v>23</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="100">
@@ -3286,7 +3146,7 @@
         <v>31</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="105">
@@ -3294,7 +3154,7 @@
         <v>33</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="106">
@@ -3984,7 +3844,7 @@
         <v>86</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>106</v>
@@ -4501,7 +4361,7 @@
         <v>86</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>106</v>
@@ -4812,7 +4672,7 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>84</v>
@@ -5848,7 +5708,7 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -7281,16 +7141,16 @@
         <v>77</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>219</v>
@@ -7388,16 +7248,16 @@
         <v>77</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>223</v>
@@ -7516,7 +7376,7 @@
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>106</v>
@@ -7561,9 +7421,7 @@
       <c r="N41" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="O41" t="s" s="2">
-        <v>233</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" s="2"/>
       <c r="Q41" t="s" s="2">
         <v>77</v>
@@ -7632,10 +7490,10 @@
         <v>168</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -7661,13 +7519,13 @@
         <v>98</v>
       </c>
       <c r="M42" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
@@ -7717,7 +7575,7 @@
         <v>77</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>78</v>
@@ -7737,14 +7595,14 @@
         <v>168</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
@@ -7763,16 +7621,16 @@
         <v>149</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
@@ -7822,7 +7680,7 @@
         <v>77</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>78</v>
@@ -7831,10 +7689,10 @@
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44">
@@ -7842,10 +7700,10 @@
         <v>168</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -7945,10 +7803,10 @@
         <v>168</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -8050,10 +7908,10 @@
         <v>168</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -8079,13 +7937,13 @@
         <v>87</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -8135,7 +7993,7 @@
         <v>77</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>78</v>
@@ -8144,7 +8002,7 @@
         <v>86</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>106</v>
@@ -8155,10 +8013,10 @@
         <v>168</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -8184,13 +8042,13 @@
         <v>98</v>
       </c>
       <c r="M47" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O47" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -8216,31 +8074,31 @@
         <v>77</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AA47" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z47" t="s" s="2">
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG47" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>78</v>
@@ -8260,10 +8118,10 @@
         <v>168</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -8289,13 +8147,13 @@
         <v>135</v>
       </c>
       <c r="M48" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
@@ -8345,7 +8203,7 @@
         <v>77</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>78</v>
@@ -8354,7 +8212,7 @@
         <v>86</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>106</v>
@@ -8365,10 +8223,10 @@
         <v>168</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -8394,13 +8252,13 @@
         <v>87</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" t="s" s="2">
@@ -8450,7 +8308,7 @@
         <v>77</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>78</v>
@@ -8470,14 +8328,14 @@
         <v>168</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" t="s" s="2">
@@ -8496,17 +8354,15 @@
         <v>149</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>274</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
         <v>77</v>
@@ -8555,7 +8411,7 @@
         <v>77</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>78</v>
@@ -8564,10 +8420,10 @@
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51">
@@ -8575,10 +8431,10 @@
         <v>168</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -8601,17 +8457,15 @@
         <v>77</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" s="2"/>
       <c r="Q51" t="s" s="2">
         <v>77</v>
@@ -8660,7 +8514,7 @@
         <v>77</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>78</v>
@@ -8669,10 +8523,10 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52">
@@ -8680,10 +8534,10 @@
         <v>168</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -8709,13 +8563,13 @@
         <v>130</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" t="s" s="2">
@@ -8723,32 +8577,32 @@
       </c>
       <c r="R52" s="2"/>
       <c r="S52" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AA52" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="T52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="AB52" t="s" s="2">
         <v>77</v>
       </c>
@@ -8765,7 +8619,7 @@
         <v>77</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>86</v>
@@ -8785,14 +8639,14 @@
         <v>168</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s" s="2">
@@ -8811,16 +8665,16 @@
         <v>149</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" t="s" s="2">
@@ -8846,13 +8700,13 @@
         <v>77</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AB53" t="s" s="2">
         <v>77</v>
@@ -8870,7 +8724,7 @@
         <v>77</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>78</v>
@@ -8879,7 +8733,7 @@
         <v>86</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>106</v>
@@ -8890,10 +8744,10 @@
         <v>168</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8916,16 +8770,16 @@
         <v>77</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" t="s" s="2">
@@ -8951,31 +8805,31 @@
         <v>77</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG54" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>78</v>
@@ -8984,7 +8838,7 @@
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>106</v>
@@ -8995,10 +8849,10 @@
         <v>168</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -9024,20 +8878,20 @@
         <v>130</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="R55" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>77</v>
@@ -9058,13 +8912,13 @@
         <v>77</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AB55" t="s" s="2">
         <v>77</v>
@@ -9082,7 +8936,7 @@
         <v>77</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>78</v>
@@ -9102,10 +8956,10 @@
         <v>168</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -9128,17 +8982,15 @@
         <v>77</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" s="2"/>
       <c r="Q56" t="s" s="2">
         <v>77</v>
@@ -9163,13 +9015,13 @@
         <v>77</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AB56" t="s" s="2">
         <v>77</v>
@@ -9187,7 +9039,7 @@
         <v>77</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>78</v>
@@ -9196,7 +9048,7 @@
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>106</v>
@@ -9207,14 +9059,14 @@
         <v>168</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" t="s" s="2">
@@ -9233,17 +9085,15 @@
         <v>149</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" s="2"/>
       <c r="Q57" t="s" s="2">
         <v>77</v>
@@ -9292,7 +9142,7 @@
         <v>77</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>78</v>
@@ -9301,10 +9151,10 @@
         <v>86</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
@@ -9312,10 +9162,10 @@
         <v>168</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -9338,16 +9188,16 @@
         <v>77</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" t="s" s="2">
@@ -9373,13 +9223,13 @@
         <v>77</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AB58" t="s" s="2">
         <v>77</v>
@@ -9397,7 +9247,7 @@
         <v>77</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>78</v>
@@ -9406,7 +9256,7 @@
         <v>86</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>106</v>
@@ -9417,10 +9267,10 @@
         <v>168</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -9443,16 +9293,16 @@
         <v>77</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
@@ -9502,7 +9352,7 @@
         <v>77</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>78</v>
@@ -9511,10 +9361,10 @@
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60">
@@ -9522,10 +9372,10 @@
         <v>168</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -9548,16 +9398,16 @@
         <v>149</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
@@ -9607,7 +9457,7 @@
         <v>77</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>78</v>
@@ -9616,10 +9466,10 @@
         <v>86</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61">
@@ -9627,10 +9477,10 @@
         <v>168</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -9656,13 +9506,13 @@
         <v>161</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
@@ -9712,7 +9562,7 @@
         <v>77</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>78</v>
@@ -9732,10 +9582,10 @@
         <v>168</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -9761,13 +9611,13 @@
         <v>161</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
@@ -9817,7 +9667,7 @@
         <v>77</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>78</v>
@@ -9837,10 +9687,10 @@
         <v>168</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -9863,16 +9713,16 @@
         <v>77</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -9922,7 +9772,7 @@
         <v>77</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>78</v>
@@ -9931,10 +9781,10 @@
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64">
@@ -9942,10 +9792,10 @@
         <v>168</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -10045,10 +9895,10 @@
         <v>168</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -10150,10 +10000,10 @@
         <v>168</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -10179,13 +10029,13 @@
         <v>87</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
@@ -10235,7 +10085,7 @@
         <v>77</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>78</v>
@@ -10244,7 +10094,7 @@
         <v>86</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>106</v>
@@ -10255,10 +10105,10 @@
         <v>168</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -10284,13 +10134,13 @@
         <v>98</v>
       </c>
       <c r="M67" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O67" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -10316,31 +10166,31 @@
         <v>77</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AA67" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z67" t="s" s="2">
+      <c r="AB67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG67" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>78</v>
@@ -10360,10 +10210,10 @@
         <v>168</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -10386,16 +10236,16 @@
         <v>149</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M68" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O68" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
@@ -10445,7 +10295,7 @@
         <v>77</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>78</v>
@@ -10454,7 +10304,7 @@
         <v>86</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>106</v>
@@ -10465,10 +10315,10 @@
         <v>168</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -10494,13 +10344,13 @@
         <v>87</v>
       </c>
       <c r="M69" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
@@ -10550,7 +10400,7 @@
         <v>77</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>78</v>
@@ -10570,10 +10420,10 @@
         <v>168</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10596,16 +10446,16 @@
         <v>77</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
@@ -10655,7 +10505,7 @@
         <v>77</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>78</v>
@@ -10664,10 +10514,10 @@
         <v>86</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71">
@@ -10675,10 +10525,10 @@
         <v>168</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10778,10 +10628,10 @@
         <v>168</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -10883,10 +10733,10 @@
         <v>168</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10912,13 +10762,13 @@
         <v>87</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -10968,7 +10818,7 @@
         <v>77</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>78</v>
@@ -10977,7 +10827,7 @@
         <v>86</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>106</v>
@@ -10988,10 +10838,10 @@
         <v>168</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -11017,13 +10867,13 @@
         <v>98</v>
       </c>
       <c r="M74" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" t="s" s="2">
@@ -11049,31 +10899,31 @@
         <v>77</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AA74" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z74" t="s" s="2">
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG74" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>78</v>
@@ -11093,10 +10943,10 @@
         <v>168</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -11119,16 +10969,16 @@
         <v>149</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="M75" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" t="s" s="2">
@@ -11178,7 +11028,7 @@
         <v>77</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>78</v>
@@ -11187,7 +11037,7 @@
         <v>86</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>106</v>
@@ -11198,10 +11048,10 @@
         <v>168</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -11227,13 +11077,13 @@
         <v>87</v>
       </c>
       <c r="M76" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" t="s" s="2">
@@ -11283,7 +11133,7 @@
         <v>77</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>78</v>
@@ -11303,10 +11153,10 @@
         <v>168</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11329,16 +11179,16 @@
         <v>149</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" t="s" s="2">
@@ -11364,13 +11214,13 @@
         <v>77</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="AA77" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AB77" t="s" s="2">
         <v>77</v>
@@ -11388,7 +11238,7 @@
         <v>77</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>78</v>
@@ -11397,7 +11247,7 @@
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>106</v>
@@ -11408,10 +11258,10 @@
         <v>168</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11434,17 +11284,15 @@
         <v>149</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" s="2"/>
       <c r="Q78" t="s" s="2">
         <v>77</v>
@@ -11493,7 +11341,7 @@
         <v>77</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>78</v>
@@ -11502,10 +11350,10 @@
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79">
@@ -11513,10 +11361,10 @@
         <v>168</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11542,10 +11390,10 @@
         <v>143</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -11596,7 +11444,7 @@
         <v>77</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>78</v>
@@ -11605,7 +11453,7 @@
         <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>106</v>
@@ -11616,10 +11464,10 @@
         <v>168</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11719,10 +11567,10 @@
         <v>168</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11792,16 +11640,16 @@
         <v>77</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD81" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>96</v>
@@ -11824,10 +11672,10 @@
         <v>168</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11931,10 +11779,10 @@
         <v>168</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11960,13 +11808,13 @@
         <v>87</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
@@ -12016,7 +11864,7 @@
         <v>77</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>86</v>
@@ -12025,7 +11873,7 @@
         <v>86</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>106</v>
@@ -12036,10 +11884,10 @@
         <v>168</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -12065,14 +11913,12 @@
         <v>164</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" s="2"/>
       <c r="Q84" t="s" s="2">
         <v>77</v>
@@ -12121,7 +11967,7 @@
         <v>77</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>78</v>
@@ -12130,7 +11976,7 @@
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>106</v>
@@ -12138,13 +11984,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="B85" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="C85" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -12170,10 +12016,10 @@
         <v>80</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
@@ -12224,7 +12070,7 @@
         <v>77</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>78</v>
@@ -12236,18 +12082,18 @@
         <v>77</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -12346,13 +12192,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -12449,13 +12295,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -12552,13 +12398,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -12657,13 +12503,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -12689,13 +12535,13 @@
         <v>180</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
@@ -12745,7 +12591,7 @@
         <v>77</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>78</v>
@@ -12762,13 +12608,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -12791,16 +12637,16 @@
         <v>149</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
@@ -12850,7 +12696,7 @@
         <v>77</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>78</v>
@@ -12867,13 +12713,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -12899,13 +12745,13 @@
         <v>98</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="P92" s="2"/>
       <c r="Q92" t="s" s="2">
@@ -12955,7 +12801,7 @@
         <v>77</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>78</v>
@@ -12972,13 +12818,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -13001,16 +12847,16 @@
         <v>149</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="P93" s="2"/>
       <c r="Q93" t="s" s="2">
@@ -13060,7 +12906,7 @@
         <v>77</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>78</v>
@@ -13077,13 +12923,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -13106,16 +12952,16 @@
         <v>149</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P94" s="2"/>
       <c r="Q94" t="s" s="2">
@@ -13141,13 +12987,13 @@
         <v>77</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AA94" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="AB94" t="s" s="2">
         <v>77</v>
@@ -13165,7 +13011,7 @@
         <v>77</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>78</v>
@@ -13182,13 +13028,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -13211,16 +13057,16 @@
         <v>149</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="P95" s="2"/>
       <c r="Q95" t="s" s="2">
@@ -13246,13 +13092,13 @@
         <v>77</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AA95" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AB95" t="s" s="2">
         <v>77</v>
@@ -13270,7 +13116,7 @@
         <v>77</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>78</v>
@@ -13287,13 +13133,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -13392,13 +13238,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -13462,7 +13308,7 @@
         <v>200</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>445</v>
+        <v>201</v>
       </c>
       <c r="AB97" t="s" s="2">
         <v>77</v>
@@ -13497,13 +13343,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13602,13 +13448,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13707,13 +13553,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -13812,19 +13658,19 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" t="s" s="2">
@@ -13843,17 +13689,15 @@
         <v>77</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>32</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" s="2"/>
       <c r="Q101" t="s" s="2">
         <v>77</v>
@@ -13911,7 +13755,7 @@
         <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>84</v>
@@ -13919,19 +13763,19 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C102" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="D102" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="D102" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="E102" t="s" s="2">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" t="s" s="2">
@@ -13950,17 +13794,15 @@
         <v>77</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" s="2"/>
       <c r="Q102" t="s" s="2">
         <v>77</v>
@@ -14026,19 +13868,19 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
@@ -14057,17 +13899,15 @@
         <v>77</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" s="2"/>
       <c r="Q103" t="s" s="2">
         <v>77</v>
@@ -14125,7 +13965,7 @@
         <v>79</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>84</v>
@@ -14133,16 +13973,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="E104" t="s" s="2">
         <v>77</v>
@@ -14164,7 +14004,7 @@
         <v>77</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>32</v>
@@ -14238,16 +14078,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E105" t="s" s="2">
         <v>77</v>
@@ -14269,7 +14109,7 @@
         <v>77</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>81</v>
@@ -14343,13 +14183,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14450,13 +14290,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14482,13 +14322,13 @@
         <v>135</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="P107" s="2"/>
       <c r="Q107" t="s" s="2">
@@ -14526,7 +14366,7 @@
         <v>77</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="AD107" s="2"/>
       <c r="AE107" t="s" s="2">
@@ -14536,7 +14376,7 @@
         <v>95</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>78</v>
@@ -14553,16 +14393,16 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C108" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="D108" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="D108" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="E108" t="s" s="2">
         <v>77</v>
@@ -14584,16 +14424,16 @@
         <v>77</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
@@ -14604,7 +14444,7 @@
         <v>77</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>77</v>
@@ -14643,7 +14483,7 @@
         <v>77</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>78</v>
@@ -14660,16 +14500,16 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="E109" t="s" s="2">
         <v>77</v>
@@ -14691,16 +14531,16 @@
         <v>77</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="P109" s="2"/>
       <c r="Q109" t="s" s="2">
@@ -14711,7 +14551,7 @@
         <v>77</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>77</v>
@@ -14750,7 +14590,7 @@
         <v>77</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>78</v>
@@ -14767,13 +14607,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -14796,16 +14636,16 @@
         <v>77</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
@@ -14855,7 +14695,7 @@
         <v>77</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>78</v>
@@ -14867,18 +14707,18 @@
         <v>83</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14904,13 +14744,13 @@
         <v>130</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="P111" s="2"/>
       <c r="Q111" t="s" s="2">
@@ -14918,7 +14758,7 @@
       </c>
       <c r="R111" s="2"/>
       <c r="S111" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>77</v>
@@ -14936,13 +14776,11 @@
         <v>77</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="Z111" s="2"/>
       <c r="AA111" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AB111" t="s" s="2">
         <v>77</v>
@@ -14960,7 +14798,7 @@
         <v>77</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>86</v>
@@ -14977,13 +14815,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -15006,13 +14844,13 @@
         <v>77</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
@@ -15039,13 +14877,13 @@
         <v>77</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="AA112" t="s" s="2">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="AB112" t="s" s="2">
         <v>77</v>
@@ -15063,7 +14901,7 @@
         <v>77</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>78</v>
@@ -15080,13 +14918,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -15109,16 +14947,16 @@
         <v>77</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="P113" s="2"/>
       <c r="Q113" t="s" s="2">
@@ -15144,13 +14982,13 @@
         <v>77</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="AA113" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AB113" t="s" s="2">
         <v>77</v>
@@ -15168,7 +15006,7 @@
         <v>77</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>78</v>
@@ -15185,13 +15023,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -15214,16 +15052,16 @@
         <v>149</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="P114" s="2"/>
       <c r="Q114" t="s" s="2">
@@ -15273,7 +15111,7 @@
         <v>77</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>86</v>
@@ -15290,13 +15128,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -15393,13 +15231,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -15498,16 +15336,16 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="E117" t="s" s="2">
         <v>77</v>
@@ -15529,13 +15367,13 @@
         <v>77</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -15603,13 +15441,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -15632,7 +15470,7 @@
         <v>77</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>87</v>
+        <v>180</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>88</v>
@@ -15698,7 +15536,7 @@
         <v>86</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>77</v>
@@ -15706,17 +15544,17 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" t="s" s="2">
@@ -15738,14 +15576,12 @@
         <v>92</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" s="2"/>
       <c r="Q119" t="s" s="2">
         <v>77</v>
@@ -15811,13 +15647,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -15857,7 +15693,7 @@
       </c>
       <c r="R120" s="2"/>
       <c r="S120" t="s" s="2">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>77</v>
@@ -15916,13 +15752,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -15951,7 +15787,7 @@
         <v>104</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>105</v>
+        <v>522</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
@@ -15963,7 +15799,7 @@
         <v>77</v>
       </c>
       <c r="T121" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="U121" t="s" s="2">
         <v>77</v>
@@ -15978,11 +15814,11 @@
         <v>77</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z121" s="2"/>
       <c r="AA121" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="AB121" t="s" s="2">
         <v>77</v>
@@ -16009,7 +15845,7 @@
         <v>86</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>83</v>
+        <v>525</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>106</v>
@@ -16017,13 +15853,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -16049,13 +15885,13 @@
         <v>87</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="P122" s="2"/>
       <c r="Q122" t="s" s="2">
@@ -16105,7 +15941,7 @@
         <v>77</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>78</v>
@@ -16114,7 +15950,7 @@
         <v>86</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>106</v>
@@ -16122,13 +15958,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -16154,13 +15990,13 @@
         <v>98</v>
       </c>
       <c r="M123" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O123" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P123" s="2"/>
       <c r="Q123" t="s" s="2">
@@ -16186,31 +16022,31 @@
         <v>77</v>
       </c>
       <c r="Y123" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AA123" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z123" t="s" s="2">
+      <c r="AB123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG123" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>78</v>
@@ -16227,13 +16063,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -16259,13 +16095,13 @@
         <v>135</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P124" s="2"/>
       <c r="Q124" t="s" s="2">
@@ -16315,7 +16151,7 @@
         <v>77</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>78</v>
@@ -16324,7 +16160,7 @@
         <v>86</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>106</v>
@@ -16332,13 +16168,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -16435,13 +16271,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -16540,13 +16376,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -16572,16 +16408,16 @@
         <v>130</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="P127" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="Q127" t="s" s="2">
         <v>77</v>
@@ -16606,13 +16442,13 @@
         <v>77</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="AA127" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AB127" t="s" s="2">
         <v>77</v>
@@ -16630,7 +16466,7 @@
         <v>77</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>78</v>
@@ -16647,13 +16483,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -16676,19 +16512,19 @@
         <v>149</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="P128" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="Q128" t="s" s="2">
         <v>77</v>
@@ -16713,13 +16549,13 @@
         <v>77</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AA128" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="AB128" t="s" s="2">
         <v>77</v>
@@ -16737,7 +16573,7 @@
         <v>77</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>78</v>
@@ -16746,7 +16582,7 @@
         <v>86</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>106</v>
@@ -16754,13 +16590,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -16786,29 +16622,29 @@
         <v>98</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="P129" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="Q129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="R129" s="2"/>
       <c r="S129" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="U129" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="V129" t="s" s="2">
         <v>77</v>
@@ -16844,7 +16680,7 @@
         <v>77</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>78</v>
@@ -16861,13 +16697,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -16893,13 +16729,13 @@
         <v>87</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
@@ -16913,7 +16749,7 @@
         <v>77</v>
       </c>
       <c r="U130" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="V130" t="s" s="2">
         <v>77</v>
@@ -16949,7 +16785,7 @@
         <v>77</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>78</v>
@@ -16966,13 +16802,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -16995,17 +16831,15 @@
         <v>149</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" s="2"/>
       <c r="Q131" t="s" s="2">
         <v>77</v>
@@ -17054,7 +16888,7 @@
         <v>77</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>78</v>
@@ -17063,21 +16897,21 @@
         <v>86</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>573</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -17100,16 +16934,16 @@
         <v>149</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
@@ -17159,7 +16993,7 @@
         <v>77</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>78</v>
@@ -17168,21 +17002,21 @@
         <v>86</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -17208,13 +17042,13 @@
         <v>87</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="P133" s="2"/>
       <c r="Q133" t="s" s="2">
@@ -17264,7 +17098,7 @@
         <v>77</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>78</v>
@@ -17281,13 +17115,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -17310,16 +17144,16 @@
         <v>149</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="P134" s="2"/>
       <c r="Q134" t="s" s="2">
@@ -17369,7 +17203,7 @@
         <v>77</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>78</v>
@@ -17381,18 +17215,18 @@
         <v>83</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -17489,13 +17323,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -17594,13 +17428,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -17626,13 +17460,13 @@
         <v>87</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="P137" s="2"/>
       <c r="Q137" t="s" s="2">
@@ -17682,7 +17516,7 @@
         <v>77</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>78</v>
@@ -17691,7 +17525,7 @@
         <v>86</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>106</v>
@@ -17699,13 +17533,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -17731,13 +17565,13 @@
         <v>98</v>
       </c>
       <c r="M138" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O138" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P138" s="2"/>
       <c r="Q138" t="s" s="2">
@@ -17763,31 +17597,31 @@
         <v>77</v>
       </c>
       <c r="Y138" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AA138" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z138" t="s" s="2">
+      <c r="AB138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG138" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>78</v>
@@ -17804,13 +17638,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -17833,16 +17667,16 @@
         <v>149</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>478</v>
+        <v>258</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>479</v>
+        <v>259</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P139" s="2"/>
       <c r="Q139" t="s" s="2">
@@ -17892,7 +17726,7 @@
         <v>77</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>78</v>
@@ -17909,13 +17743,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -17941,13 +17775,13 @@
         <v>87</v>
       </c>
       <c r="M140" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O140" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P140" s="2"/>
       <c r="Q140" t="s" s="2">
@@ -17997,7 +17831,7 @@
         <v>77</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>78</v>
@@ -18014,13 +17848,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -18043,16 +17877,16 @@
         <v>77</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="P141" s="2"/>
       <c r="Q141" t="s" s="2">
@@ -18102,7 +17936,7 @@
         <v>77</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>78</v>
@@ -18114,18 +17948,18 @@
         <v>83</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -18148,16 +17982,16 @@
         <v>77</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>599</v>
+        <v>269</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="P142" s="2"/>
       <c r="Q142" t="s" s="2">
@@ -18207,7 +18041,7 @@
         <v>77</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>78</v>
@@ -18219,18 +18053,18 @@
         <v>83</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -18256,10 +18090,10 @@
         <v>143</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
@@ -18310,7 +18144,7 @@
         <v>77</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>78</v>
@@ -18327,13 +18161,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -18430,13 +18264,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -18535,13 +18369,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -18642,13 +18476,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -18671,19 +18505,19 @@
         <v>77</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>312</v>
+        <v>602</v>
       </c>
       <c r="P147" t="s" s="2">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="Q147" t="s" s="2">
         <v>77</v>
@@ -18708,13 +18542,13 @@
         <v>77</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="AA147" t="s" s="2">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="AB147" t="s" s="2">
         <v>77</v>
@@ -18732,7 +18566,7 @@
         <v>77</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>78</v>
@@ -18749,13 +18583,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -18778,16 +18612,16 @@
         <v>77</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="P148" s="2"/>
       <c r="Q148" t="s" s="2">
@@ -18837,7 +18671,7 @@
         <v>77</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>86</v>
@@ -18849,18 +18683,18 @@
         <v>83</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -18957,13 +18791,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -19062,13 +18896,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -19094,13 +18928,13 @@
         <v>87</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="P151" s="2"/>
       <c r="Q151" t="s" s="2">
@@ -19150,7 +18984,7 @@
         <v>77</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>78</v>
@@ -19159,7 +18993,7 @@
         <v>86</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>106</v>
@@ -19167,13 +19001,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -19199,13 +19033,13 @@
         <v>98</v>
       </c>
       <c r="M152" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O152" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P152" s="2"/>
       <c r="Q152" t="s" s="2">
@@ -19231,31 +19065,31 @@
         <v>77</v>
       </c>
       <c r="Y152" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AA152" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z152" t="s" s="2">
+      <c r="AB152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG152" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>78</v>
@@ -19272,13 +19106,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -19301,16 +19135,16 @@
         <v>149</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="M153" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O153" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P153" s="2"/>
       <c r="Q153" t="s" s="2">
@@ -19360,7 +19194,7 @@
         <v>77</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>78</v>
@@ -19369,7 +19203,7 @@
         <v>86</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>106</v>
@@ -19377,13 +19211,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -19409,13 +19243,13 @@
         <v>87</v>
       </c>
       <c r="M154" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O154" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P154" s="2"/>
       <c r="Q154" t="s" s="2">
@@ -19465,7 +19299,7 @@
         <v>77</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>78</v>
@@ -19482,13 +19316,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -19511,16 +19345,16 @@
         <v>77</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="P155" s="2"/>
       <c r="Q155" t="s" s="2">
@@ -19570,7 +19404,7 @@
         <v>77</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>78</v>
@@ -19582,18 +19416,18 @@
         <v>83</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -19616,16 +19450,16 @@
         <v>77</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="P156" s="2"/>
       <c r="Q156" t="s" s="2">
@@ -19675,7 +19509,7 @@
         <v>77</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>78</v>
@@ -19687,18 +19521,18 @@
         <v>83</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -19795,13 +19629,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -19900,13 +19734,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -19932,13 +19766,13 @@
         <v>87</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="P159" s="2"/>
       <c r="Q159" t="s" s="2">
@@ -19988,7 +19822,7 @@
         <v>77</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>78</v>
@@ -19997,7 +19831,7 @@
         <v>86</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>106</v>
@@ -20005,13 +19839,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -20037,13 +19871,13 @@
         <v>98</v>
       </c>
       <c r="M160" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O160" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P160" s="2"/>
       <c r="Q160" t="s" s="2">
@@ -20069,31 +19903,31 @@
         <v>77</v>
       </c>
       <c r="Y160" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AA160" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="Z160" t="s" s="2">
+      <c r="AB160" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG160" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>78</v>
@@ -20110,13 +19944,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -20142,13 +19976,13 @@
         <v>135</v>
       </c>
       <c r="M161" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O161" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P161" s="2"/>
       <c r="Q161" t="s" s="2">
@@ -20198,7 +20032,7 @@
         <v>77</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>78</v>
@@ -20215,13 +20049,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -20247,13 +20081,13 @@
         <v>87</v>
       </c>
       <c r="M162" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O162" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="P162" s="2"/>
       <c r="Q162" t="s" s="2">
@@ -20303,7 +20137,7 @@
         <v>77</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>78</v>
@@ -20320,13 +20154,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -20349,16 +20183,16 @@
         <v>77</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>312</v>
+        <v>602</v>
       </c>
       <c r="P163" s="2"/>
       <c r="Q163" t="s" s="2">
@@ -20384,13 +20218,13 @@
         <v>77</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="AA163" t="s" s="2">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="AB163" t="s" s="2">
         <v>77</v>
@@ -20408,7 +20242,7 @@
         <v>77</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>78</v>
@@ -20425,13 +20259,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -20454,16 +20288,16 @@
         <v>77</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="P164" s="2"/>
       <c r="Q164" t="s" s="2">
@@ -20513,7 +20347,7 @@
         <v>77</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>78</v>
@@ -20525,18 +20359,18 @@
         <v>83</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -20559,16 +20393,16 @@
         <v>77</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -20618,7 +20452,7 @@
         <v>77</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>78</v>
@@ -20630,18 +20464,18 @@
         <v>83</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -20667,10 +20501,10 @@
         <v>161</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
@@ -20721,7 +20555,7 @@
         <v>77</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>78</v>
@@ -20738,13 +20572,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -20770,10 +20604,10 @@
         <v>161</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
@@ -20824,7 +20658,7 @@
         <v>77</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>78</v>
@@ -20836,18 +20670,18 @@
         <v>77</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>658</v>
+        <v>650</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -20870,16 +20704,16 @@
         <v>77</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
@@ -20929,7 +20763,7 @@
         <v>77</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>78</v>
@@ -20941,18 +20775,18 @@
         <v>83</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -20975,16 +20809,16 @@
         <v>77</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="P169" s="2"/>
       <c r="Q169" t="s" s="2">
@@ -21034,7 +20868,7 @@
         <v>77</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>78</v>
@@ -21046,18 +20880,18 @@
         <v>83</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -21083,13 +20917,13 @@
         <v>164</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>391</v>
+        <v>661</v>
       </c>
       <c r="P170" s="2"/>
       <c r="Q170" t="s" s="2">
@@ -21139,7 +20973,7 @@
         <v>77</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>78</v>
@@ -21156,13 +20990,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -21185,16 +21019,16 @@
         <v>77</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="P171" s="2"/>
       <c r="Q171" t="s" s="2">
@@ -21244,7 +21078,7 @@
         <v>77</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>78</v>
@@ -21253,21 +21087,21 @@
         <v>79</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>673</v>
+        <v>106</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -21293,13 +21127,13 @@
         <v>143</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="P172" s="2"/>
       <c r="Q172" t="s" s="2">
@@ -21349,7 +21183,7 @@
         <v>77</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>78</v>
@@ -21366,13 +21200,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -21469,13 +21303,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -21574,13 +21408,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -21681,13 +21515,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -21710,13 +21544,13 @@
         <v>77</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" s="2"/>
@@ -21767,7 +21601,7 @@
         <v>77</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>86</v>
@@ -21784,13 +21618,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -21813,16 +21647,16 @@
         <v>77</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>312</v>
+        <v>602</v>
       </c>
       <c r="P177" s="2"/>
       <c r="Q177" t="s" s="2">
@@ -21848,13 +21682,13 @@
         <v>77</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="AA177" t="s" s="2">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="AB177" t="s" s="2">
         <v>77</v>
@@ -21872,7 +21706,7 @@
         <v>77</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>78</v>
@@ -21889,13 +21723,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -21918,16 +21752,16 @@
         <v>77</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>312</v>
+        <v>602</v>
       </c>
       <c r="P178" s="2"/>
       <c r="Q178" t="s" s="2">
@@ -21953,13 +21787,13 @@
         <v>77</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="AA178" t="s" s="2">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="AB178" t="s" s="2">
         <v>77</v>
@@ -21977,7 +21811,7 @@
         <v>77</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>78</v>
@@ -21994,13 +21828,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -22023,16 +21857,16 @@
         <v>77</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="P179" s="2"/>
       <c r="Q179" t="s" s="2">
@@ -22082,7 +21916,7 @@
         <v>77</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>78</v>
@@ -22094,22 +21928,22 @@
         <v>83</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="F180" s="2"/>
       <c r="G180" t="s" s="2">
@@ -22128,16 +21962,16 @@
         <v>77</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="P180" s="2"/>
       <c r="Q180" t="s" s="2">
@@ -22187,7 +22021,7 @@
         <v>77</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>78</v>
@@ -22199,18 +22033,18 @@
         <v>83</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -22233,16 +22067,16 @@
         <v>77</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="P181" s="2"/>
       <c r="Q181" t="s" s="2">
@@ -22292,7 +22126,7 @@
         <v>77</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>78</v>
@@ -22304,7 +22138,7 @@
         <v>83</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>244</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
